--- a/results/uci__age-group__primary-care-screening/results.xlsx
+++ b/results/uci__age-group__primary-care-screening/results.xlsx
@@ -25,13 +25,14 @@
     <sheet name="pareto" sheetId="16" r:id="rId16"/>
     <sheet name="representation" sheetId="17" r:id="rId17"/>
     <sheet name="shap_by_group" sheetId="18" r:id="rId18"/>
+    <sheet name="lime_shap_agreement" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="451">
   <si>
     <t>Value</t>
   </si>
@@ -543,12 +544,18 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
@@ -558,12 +565,18 @@
     <t>0.909 ± 0.005</t>
   </si>
   <si>
+    <t>0.915 ± 0.001</t>
+  </si>
+  <si>
     <t>0.914 ± 0.002</t>
   </si>
   <si>
     <t>0.892 ± 0.009</t>
   </si>
   <si>
+    <t>0.915 ± 0.005</t>
+  </si>
+  <si>
     <t>0.888 ± 0.015</t>
   </si>
   <si>
@@ -573,6 +586,9 @@
     <t>0.938 ± 0.005</t>
   </si>
   <si>
+    <t>0.939 ± 0.004</t>
+  </si>
+  <si>
     <t>0.940 ± 0.002</t>
   </si>
   <si>
@@ -591,9 +607,15 @@
     <t>0.903 ± 0.009</t>
   </si>
   <si>
+    <t>0.908 ± 0.004</t>
+  </si>
+  <si>
     <t>0.887 ± 0.007</t>
   </si>
   <si>
+    <t>0.902 ± 0.011</t>
+  </si>
+  <si>
     <t>0.884 ± 0.010</t>
   </si>
   <si>
@@ -603,9 +625,15 @@
     <t>0.921 ± 0.006</t>
   </si>
   <si>
+    <t>0.931 ± 0.001</t>
+  </si>
+  <si>
     <t>0.911 ± 0.008</t>
   </si>
   <si>
+    <t>0.928 ± 0.007</t>
+  </si>
+  <si>
     <t>0.906 ± 0.015</t>
   </si>
   <si>
@@ -618,6 +646,9 @@
     <t>0.944 ± 0.006</t>
   </si>
   <si>
+    <t>0.947 ± 0.004</t>
+  </si>
+  <si>
     <t>0.947 ± 0.003</t>
   </si>
   <si>
@@ -654,12 +685,18 @@
     <t>0.872 ± 0.005</t>
   </si>
   <si>
+    <t>0.862 ± 0.002</t>
+  </si>
+  <si>
     <t>0.861 ± 0.004</t>
   </si>
   <si>
     <t>0.832 ± 0.014</t>
   </si>
   <si>
+    <t>0.873 ± 0.005</t>
+  </si>
+  <si>
     <t>0.834 ± 0.019</t>
   </si>
   <si>
@@ -669,12 +706,18 @@
     <t>0.917 ± 0.003</t>
   </si>
   <si>
+    <t>0.913 ± 0.003</t>
+  </si>
+  <si>
     <t>0.916 ± 0.004</t>
   </si>
   <si>
     <t>0.902 ± 0.009</t>
   </si>
   <si>
+    <t>0.917 ± 0.005</t>
+  </si>
+  <si>
     <t>0.902 ± 0.014</t>
   </si>
   <si>
@@ -687,12 +730,18 @@
     <t>0.896 ± 0.011</t>
   </si>
   <si>
+    <t>0.888 ± 0.005</t>
+  </si>
+  <si>
     <t>0.892 ± 0.007</t>
   </si>
   <si>
     <t>0.864 ± 0.011</t>
   </si>
   <si>
+    <t>0.902 ± 0.015</t>
+  </si>
+  <si>
     <t>0.858 ± 0.007</t>
   </si>
   <si>
@@ -702,15 +751,24 @@
     <t>0.923 ± 0.005</t>
   </si>
   <si>
+    <t>0.926 ± 0.001</t>
+  </si>
+  <si>
     <t>0.925 ± 0.002</t>
   </si>
   <si>
     <t>0.905 ± 0.009</t>
   </si>
   <si>
+    <t>0.927 ± 0.004</t>
+  </si>
+  <si>
     <t>0.950 ± 0.003</t>
   </si>
   <si>
+    <t>0.949 ± 0.003</t>
+  </si>
+  <si>
     <t>0.949 ± 0.002</t>
   </si>
   <si>
@@ -726,24 +784,36 @@
     <t>0.920 ± 0.008</t>
   </si>
   <si>
+    <t>0.923 ± 0.004</t>
+  </si>
+  <si>
     <t>0.917 ± 0.007</t>
   </si>
   <si>
     <t>0.905 ± 0.006</t>
   </si>
   <si>
+    <t>0.919 ± 0.010</t>
+  </si>
+  <si>
     <t>0.283 ± 0.004</t>
   </si>
   <si>
     <t>0.246 ± 0.005</t>
   </si>
   <si>
+    <t>0.274 ± 0.002</t>
+  </si>
+  <si>
     <t>0.275 ± 0.004</t>
   </si>
   <si>
     <t>0.220 ± 0.024</t>
   </si>
   <si>
+    <t>0.253 ± 0.013</t>
+  </si>
+  <si>
     <t>0.222 ± 0.021</t>
   </si>
   <si>
@@ -756,12 +826,18 @@
     <t>0.243 ± 0.006</t>
   </si>
   <si>
+    <t>0.254 ± 0.002</t>
+  </si>
+  <si>
     <t>0.254 ± 0.006</t>
   </si>
   <si>
     <t>0.235 ± 0.014</t>
   </si>
   <si>
+    <t>0.247 ± 0.008</t>
+  </si>
+  <si>
     <t>0.233 ± 0.006</t>
   </si>
   <si>
@@ -774,12 +850,18 @@
     <t>0.222 ± 0.014</t>
   </si>
   <si>
+    <t>0.231 ± 0.011</t>
+  </si>
+  <si>
     <t>0.255 ± 0.021</t>
   </si>
   <si>
     <t>0.208 ± 0.007</t>
   </si>
   <si>
+    <t>0.209 ± 0.022</t>
+  </si>
+  <si>
     <t>0.205 ± 0.011</t>
   </si>
   <si>
@@ -792,12 +874,18 @@
     <t>0.649 ± 0.007</t>
   </si>
   <si>
+    <t>0.609 ± 0.003</t>
+  </si>
+  <si>
     <t>0.608 ± 0.005</t>
   </si>
   <si>
     <t>0.664 ± 0.025</t>
   </si>
   <si>
+    <t>0.640 ± 0.018</t>
+  </si>
+  <si>
     <t>0.665 ± 0.023</t>
   </si>
   <si>
@@ -810,12 +898,18 @@
     <t>0.666 ± 0.008</t>
   </si>
   <si>
+    <t>0.651 ± 0.003</t>
+  </si>
+  <si>
     <t>0.652 ± 0.006</t>
   </si>
   <si>
     <t>0.670 ± 0.013</t>
   </si>
   <si>
+    <t>0.661 ± 0.010</t>
+  </si>
+  <si>
     <t>0.675 ± 0.006</t>
   </si>
   <si>
@@ -828,12 +922,18 @@
     <t>0.693 ± 0.015</t>
   </si>
   <si>
+    <t>0.676 ± 0.012</t>
+  </si>
+  <si>
     <t>0.656 ± 0.023</t>
   </si>
   <si>
     <t>0.699 ± 0.009</t>
   </si>
   <si>
+    <t>0.712 ± 0.025</t>
+  </si>
+  <si>
     <t>0.701 ± 0.014</t>
   </si>
   <si>
@@ -846,12 +946,18 @@
     <t>0.052 ± 0.010</t>
   </si>
   <si>
+    <t>0.071 ± 0.004</t>
+  </si>
+  <si>
     <t>0.072 ± 0.007</t>
   </si>
   <si>
     <t>0.020 ± 0.023</t>
   </si>
   <si>
+    <t>0.050 ± 0.011</t>
+  </si>
+  <si>
     <t>0.017 ± 0.012</t>
   </si>
   <si>
@@ -861,12 +967,18 @@
     <t>0.029 ± 0.006</t>
   </si>
   <si>
+    <t>0.037 ± 0.006</t>
+  </si>
+  <si>
     <t>0.036 ± 0.004</t>
   </si>
   <si>
     <t>0.015 ± 0.012</t>
   </si>
   <si>
+    <t>0.029 ± 0.010</t>
+  </si>
+  <si>
     <t>0.010 ± 0.009</t>
   </si>
   <si>
@@ -879,15 +991,24 @@
     <t>0.025 ± 0.012</t>
   </si>
   <si>
+    <t>0.037 ± 0.009</t>
+  </si>
+  <si>
     <t>0.043 ± 0.012</t>
   </si>
   <si>
     <t>0.014 ± 0.009</t>
   </si>
   <si>
+    <t>0.014 ± 0.010</t>
+  </si>
+  <si>
     <t>0.038 ± 0.024</t>
   </si>
   <si>
+    <t>0.053 ± 0.007</t>
+  </si>
+  <si>
     <t>0.038 ± 0.014</t>
   </si>
   <si>
@@ -897,6 +1018,9 @@
     <t>0.029 ± 0.009</t>
   </si>
   <si>
+    <t>0.036 ± 0.005</t>
+  </si>
+  <si>
     <t>0.030 ± 0.014</t>
   </si>
   <si>
@@ -906,12 +1030,18 @@
     <t>0.043 ± 0.030</t>
   </si>
   <si>
+    <t>0.050 ± 0.021</t>
+  </si>
+  <si>
     <t>0.079 ± 0.018</t>
   </si>
   <si>
     <t>0.022 ± 0.009</t>
   </si>
   <si>
+    <t>0.056 ± 0.041</t>
+  </si>
+  <si>
     <t>0.028 ± 0.014</t>
   </si>
   <si>
@@ -921,6 +1051,9 @@
     <t>0.008 ± 0.008</t>
   </si>
   <si>
+    <t>0.024 ± 0.020</t>
+  </si>
+  <si>
     <t>0.021 ± 0.016</t>
   </si>
   <si>
@@ -933,12 +1066,18 @@
     <t>0.038 ± 0.013</t>
   </si>
   <si>
+    <t>0.025 ± 0.007</t>
+  </si>
+  <si>
     <t>0.024 ± 0.007</t>
   </si>
   <si>
     <t>0.028 ± 0.009</t>
   </si>
   <si>
+    <t>0.031 ± 0.010</t>
+  </si>
+  <si>
     <t>0.031 ± 0.015</t>
   </si>
   <si>
@@ -951,12 +1090,18 @@
     <t>0.070 ± 0.021</t>
   </si>
   <si>
+    <t>0.062 ± 0.014</t>
+  </si>
+  <si>
     <t>0.038 ± 0.036</t>
   </si>
   <si>
     <t>0.051 ± 0.024</t>
   </si>
   <si>
+    <t>0.082 ± 0.028</t>
+  </si>
+  <si>
     <t>0.051 ± 0.018</t>
   </si>
   <si>
@@ -969,12 +1114,18 @@
     <t>0.018 ± 0.009</t>
   </si>
   <si>
+    <t>0.010 ± 0.002</t>
+  </si>
+  <si>
     <t>0.011 ± 0.004</t>
   </si>
   <si>
     <t>0.053 ± 0.025</t>
   </si>
   <si>
+    <t>0.010 ± 0.008</t>
+  </si>
+  <si>
     <t>0.041 ± 0.026</t>
   </si>
   <si>
@@ -987,12 +1138,18 @@
     <t>0.015 ± 0.008</t>
   </si>
   <si>
+    <t>0.013 ± 0.006</t>
+  </si>
+  <si>
     <t>0.012 ± 0.004</t>
   </si>
   <si>
     <t>0.009 ± 0.009</t>
   </si>
   <si>
+    <t>0.012 ± 0.006</t>
+  </si>
+  <si>
     <t>0.011 ± 0.009</t>
   </si>
   <si>
@@ -1002,12 +1159,18 @@
     <t>0.020 ± 0.014</t>
   </si>
   <si>
+    <t>0.023 ± 0.009</t>
+  </si>
+  <si>
     <t>0.017 ± 0.016</t>
   </si>
   <si>
     <t>0.023 ± 0.018</t>
   </si>
   <si>
+    <t>0.020 ± 0.015</t>
+  </si>
+  <si>
     <t>0.024 ± 0.010</t>
   </si>
   <si>
@@ -1035,12 +1198,18 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
@@ -1050,12 +1219,18 @@
     <t>[-0.038, 0.045]</t>
   </si>
   <si>
+    <t>[-0.026, 0.000]</t>
+  </si>
+  <si>
     <t>[-0.040, 0.007]</t>
   </si>
   <si>
     <t>[-0.102, 0.058]</t>
   </si>
   <si>
+    <t>[-0.051, 0.033]</t>
+  </si>
+  <si>
     <t>[-0.092, 0.038]</t>
   </si>
   <si>
@@ -1071,6 +1246,9 @@
     <t>[-0.032, 0.037]</t>
   </si>
   <si>
+    <t>[0.000, 0.025]</t>
+  </si>
+  <si>
     <t>[-0.048, 0.088]</t>
   </si>
   <si>
@@ -1080,12 +1258,18 @@
     <t>[-0.035, 0.074]</t>
   </si>
   <si>
+    <t>[-0.037, 0.083]</t>
+  </si>
+  <si>
     <t>[-0.009, 0.040]</t>
   </si>
   <si>
     <t>[-0.092, 0.075]</t>
   </si>
   <si>
+    <t>[-0.030, 0.101]</t>
+  </si>
+  <si>
     <t>[-0.091, 0.071]</t>
   </si>
   <si>
@@ -1095,6 +1279,9 @@
     <t>[-0.030, 0.002]</t>
   </si>
   <si>
+    <t>[0.000, 0.007]</t>
+  </si>
+  <si>
     <t>[0.000, 0.010]</t>
   </si>
   <si>
@@ -1113,6 +1300,9 @@
     <t>[-0.026, -0.002]</t>
   </si>
   <si>
+    <t>[-0.011, 0.000]</t>
+  </si>
+  <si>
     <t>[-0.029, -0.004]</t>
   </si>
   <si>
@@ -1122,12 +1312,18 @@
     <t>[-0.017, 0.006]</t>
   </si>
   <si>
+    <t>[-0.003, 0.028]</t>
+  </si>
+  <si>
     <t>[-0.018, 0.000]</t>
   </si>
   <si>
     <t>[-0.035, 0.010]</t>
   </si>
   <si>
+    <t>[-0.027, 0.003]</t>
+  </si>
+  <si>
     <t>[-0.036, 0.003]</t>
   </si>
   <si>
@@ -1152,22 +1348,22 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
-    <t>0.893 ± 0.011</t>
-  </si>
-  <si>
-    <t>0.908 ± 0.001</t>
-  </si>
-  <si>
-    <t>0.843 ± 0.041</t>
-  </si>
-  <si>
-    <t>0.043 ± 0.011</t>
+    <t>0.894 ± 0.013</t>
+  </si>
+  <si>
+    <t>0.909 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.845 ± 0.044</t>
+  </si>
+  <si>
+    <t>0.039 ± 0.017</t>
   </si>
   <si>
     <t>0.084 ± 0.000</t>
   </si>
   <si>
-    <t>0.212 ± 0.042</t>
+    <t>0.210 ± 0.039</t>
   </si>
   <si>
     <t>0.281 ± 0.000</t>
@@ -1183,6 +1379,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1648,7 +1850,7 @@
         <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F2" t="s">
         <v>81</v>
@@ -1657,19 +1859,19 @@
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="I2" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="J2" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="K2" t="s">
         <v>134</v>
       </c>
       <c r="L2" t="s">
-        <v>309</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1677,34 +1879,34 @@
         <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F3" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="G3" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H3" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="I3" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="J3" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K3" t="s">
         <v>134</v>
       </c>
       <c r="L3" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1712,34 +1914,34 @@
         <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="G4" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H4" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="I4" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="J4" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="K4" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="L4" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1747,34 +1949,34 @@
         <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F5" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="G5" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="H5" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="I5" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="J5" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="K5" t="s">
         <v>134</v>
       </c>
       <c r="L5" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1782,34 +1984,34 @@
         <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="G6" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="H6" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="I6" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="J6" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="K6" t="s">
-        <v>295</v>
+        <v>134</v>
       </c>
       <c r="L6" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1817,467 +2019,677 @@
         <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F7" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="G7" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="H7" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="I7" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="J7" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="K7" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="L7" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="F8" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="G8" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H8" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>307</v>
       </c>
       <c r="J8" t="s">
-        <v>127</v>
+        <v>324</v>
       </c>
       <c r="K8" t="s">
-        <v>297</v>
+        <v>339</v>
       </c>
       <c r="L8" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="H9" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="I9" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="J9" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="K9" t="s">
-        <v>298</v>
+        <v>340</v>
       </c>
       <c r="L9" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E10" t="s">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="G10" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="H10" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="I10" t="s">
-        <v>275</v>
+        <v>127</v>
       </c>
       <c r="J10" t="s">
-        <v>286</v>
+        <v>127</v>
       </c>
       <c r="K10" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="L10" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F11" t="s">
-        <v>226</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="H11" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="I11" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="J11" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="K11" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="L11" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D12" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="G12" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="H12" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="I12" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="J12" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="K12" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="L12" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E13" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="G13" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="H13" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="I13" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="J13" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="K13" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="L13" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>60</v>
-      </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E14" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F14" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="G14" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="H14" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="I14" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="J14" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="K14" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="L14" t="s">
-        <v>273</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F15" t="s">
-        <v>229</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="H15" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="I15" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="J15" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="K15" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="L15" t="s">
-        <v>321</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" t="s">
+        <v>267</v>
+      </c>
+      <c r="H16" t="s">
+        <v>291</v>
+      </c>
+      <c r="I16" t="s">
+        <v>314</v>
+      </c>
+      <c r="J16" t="s">
+        <v>328</v>
+      </c>
+      <c r="K16" t="s">
+        <v>347</v>
+      </c>
+      <c r="L16" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" t="s">
+        <v>246</v>
+      </c>
+      <c r="G17" t="s">
+        <v>268</v>
+      </c>
+      <c r="H17" t="s">
+        <v>292</v>
+      </c>
+      <c r="I17" t="s">
+        <v>315</v>
+      </c>
+      <c r="J17" t="s">
+        <v>329</v>
+      </c>
+      <c r="K17" t="s">
+        <v>348</v>
+      </c>
+      <c r="L17" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" t="s">
+        <v>229</v>
+      </c>
+      <c r="F18" t="s">
+        <v>247</v>
+      </c>
+      <c r="G18" t="s">
+        <v>269</v>
+      </c>
+      <c r="H18" t="s">
+        <v>293</v>
+      </c>
+      <c r="I18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J18" t="s">
+        <v>330</v>
+      </c>
+      <c r="K18" t="s">
+        <v>349</v>
+      </c>
+      <c r="L18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="B19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" t="s">
+        <v>248</v>
+      </c>
+      <c r="G19" t="s">
+        <v>270</v>
+      </c>
+      <c r="H19" t="s">
+        <v>294</v>
+      </c>
+      <c r="I19" t="s">
+        <v>317</v>
+      </c>
+      <c r="J19" t="s">
+        <v>317</v>
+      </c>
+      <c r="K19" t="s">
+        <v>350</v>
+      </c>
+      <c r="L19" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="B20" t="s">
         <v>169</v>
       </c>
-      <c r="C16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" t="s">
-        <v>200</v>
-      </c>
-      <c r="E16" t="s">
-        <v>217</v>
-      </c>
-      <c r="F16" t="s">
-        <v>230</v>
-      </c>
-      <c r="G16" t="s">
-        <v>246</v>
-      </c>
-      <c r="H16" t="s">
-        <v>264</v>
-      </c>
-      <c r="I16" t="s">
-        <v>281</v>
-      </c>
-      <c r="J16" t="s">
-        <v>290</v>
-      </c>
-      <c r="K16" t="s">
-        <v>305</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="C20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" t="s">
+        <v>231</v>
+      </c>
+      <c r="F20" t="s">
+        <v>249</v>
+      </c>
+      <c r="G20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H20" t="s">
+        <v>295</v>
+      </c>
+      <c r="I20" t="s">
+        <v>318</v>
+      </c>
+      <c r="J20" t="s">
+        <v>331</v>
+      </c>
+      <c r="K20" t="s">
+        <v>351</v>
+      </c>
+      <c r="L20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="B21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" t="s">
+        <v>250</v>
+      </c>
+      <c r="G21" t="s">
+        <v>272</v>
+      </c>
+      <c r="H21" t="s">
+        <v>296</v>
+      </c>
+      <c r="I21" t="s">
+        <v>319</v>
+      </c>
+      <c r="J21" t="s">
+        <v>332</v>
+      </c>
+      <c r="K21" t="s">
+        <v>352</v>
+      </c>
+      <c r="L21" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E22" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" t="s">
+        <v>251</v>
+      </c>
+      <c r="G22" t="s">
+        <v>273</v>
+      </c>
+      <c r="H22" t="s">
+        <v>297</v>
+      </c>
+      <c r="I22" t="s">
+        <v>320</v>
+      </c>
+      <c r="J22" t="s">
+        <v>333</v>
+      </c>
+      <c r="K22" t="s">
+        <v>353</v>
+      </c>
+      <c r="L22" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" t="s">
+        <v>212</v>
+      </c>
+      <c r="E23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F23" t="s">
+        <v>252</v>
+      </c>
+      <c r="G23" t="s">
+        <v>274</v>
+      </c>
+      <c r="H23" t="s">
+        <v>298</v>
+      </c>
+      <c r="I23" t="s">
+        <v>321</v>
+      </c>
+      <c r="J23" t="s">
+        <v>334</v>
+      </c>
+      <c r="K23" t="s">
+        <v>354</v>
+      </c>
+      <c r="L23" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="B24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" t="s">
+        <v>253</v>
+      </c>
+      <c r="G24" t="s">
+        <v>275</v>
+      </c>
+      <c r="H24" t="s">
+        <v>299</v>
+      </c>
+      <c r="I24" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" t="s">
-        <v>218</v>
-      </c>
-      <c r="F17" t="s">
-        <v>231</v>
-      </c>
-      <c r="G17" t="s">
-        <v>247</v>
-      </c>
-      <c r="H17" t="s">
-        <v>265</v>
-      </c>
-      <c r="I17" t="s">
-        <v>282</v>
-      </c>
-      <c r="J17" t="s">
-        <v>291</v>
-      </c>
-      <c r="K17" t="s">
-        <v>306</v>
-      </c>
-      <c r="L17" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" t="s">
-        <v>186</v>
-      </c>
-      <c r="D18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E18" t="s">
-        <v>219</v>
-      </c>
-      <c r="F18" t="s">
-        <v>232</v>
-      </c>
-      <c r="G18" t="s">
-        <v>248</v>
-      </c>
-      <c r="H18" t="s">
-        <v>266</v>
-      </c>
-      <c r="I18" t="s">
-        <v>283</v>
-      </c>
-      <c r="J18" t="s">
-        <v>292</v>
-      </c>
-      <c r="K18" t="s">
-        <v>307</v>
-      </c>
-      <c r="L18" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" t="s">
-        <v>203</v>
-      </c>
-      <c r="E19" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" t="s">
-        <v>199</v>
-      </c>
-      <c r="G19" t="s">
-        <v>249</v>
-      </c>
-      <c r="H19" t="s">
-        <v>267</v>
-      </c>
-      <c r="I19" t="s">
-        <v>283</v>
-      </c>
-      <c r="J19" t="s">
-        <v>293</v>
-      </c>
-      <c r="K19" t="s">
-        <v>308</v>
-      </c>
-      <c r="L19" t="s">
-        <v>325</v>
+      <c r="J24" t="s">
+        <v>335</v>
+      </c>
+      <c r="K24" t="s">
+        <v>355</v>
+      </c>
+      <c r="L24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="B25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E25" t="s">
+        <v>236</v>
+      </c>
+      <c r="F25" t="s">
+        <v>209</v>
+      </c>
+      <c r="G25" t="s">
+        <v>276</v>
+      </c>
+      <c r="H25" t="s">
+        <v>300</v>
+      </c>
+      <c r="I25" t="s">
+        <v>321</v>
+      </c>
+      <c r="J25" t="s">
+        <v>336</v>
+      </c>
+      <c r="K25" t="s">
+        <v>356</v>
+      </c>
+      <c r="L25" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="A18:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2285,7 +2697,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2373,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2384,16 +2796,16 @@
         <v>171</v>
       </c>
       <c r="C6">
-        <v>0.829</v>
+        <v>0.898</v>
       </c>
       <c r="D6">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.835</v>
+        <v>0.826</v>
       </c>
       <c r="F6">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2401,33 +2813,30 @@
         <v>172</v>
       </c>
       <c r="C7">
-        <v>0.836</v>
+        <v>0.829</v>
       </c>
       <c r="D7">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="E7">
-        <v>0.832</v>
+        <v>0.835</v>
       </c>
       <c r="F7">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C8">
-        <v>0.9320000000000001</v>
+        <v>0.898</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.897</v>
+        <v>0.848</v>
       </c>
       <c r="F8">
         <v>0.022</v>
@@ -2435,24 +2844,27 @@
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C9">
-        <v>0.9320000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="E9">
-        <v>0.85</v>
+        <v>0.832</v>
       </c>
       <c r="F9">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>0.9320000000000001</v>
@@ -2461,173 +2873,275 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.903</v>
+        <v>0.897</v>
       </c>
       <c r="F10">
-        <v>0.038</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11">
-        <v>0.9340000000000001</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D11">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.898</v>
+        <v>0.85</v>
       </c>
       <c r="F11">
-        <v>0.026</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C12">
-        <v>0.908</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D12">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.895</v>
+        <v>0.903</v>
       </c>
       <c r="F12">
-        <v>0.031</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C13">
-        <v>0.907</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D13">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.897</v>
+        <v>0.895</v>
       </c>
       <c r="F13">
-        <v>0.04</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>60</v>
-      </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C14">
-        <v>0.917</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D14">
-        <v>0.139</v>
+        <v>0.006</v>
       </c>
       <c r="E14">
-        <v>0.871</v>
+        <v>0.898</v>
       </c>
       <c r="F14">
-        <v>0.06900000000000001</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C15">
-        <v>0.929</v>
+        <v>0.908</v>
       </c>
       <c r="D15">
-        <v>0.097</v>
+        <v>0.012</v>
       </c>
       <c r="E15">
-        <v>0.839</v>
+        <v>0.895</v>
       </c>
       <c r="F15">
-        <v>0.076</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0.903</v>
+      </c>
+      <c r="F16">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17">
+        <v>0.907</v>
+      </c>
+      <c r="D17">
+        <v>0.03</v>
+      </c>
+      <c r="E17">
+        <v>0.897</v>
+      </c>
+      <c r="F17">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18">
+        <v>0.917</v>
+      </c>
+      <c r="D18">
+        <v>0.139</v>
+      </c>
+      <c r="E18">
+        <v>0.871</v>
+      </c>
+      <c r="F18">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="B19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19">
+        <v>0.929</v>
+      </c>
+      <c r="D19">
+        <v>0.097</v>
+      </c>
+      <c r="E19">
+        <v>0.839</v>
+      </c>
+      <c r="F19">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" t="s">
         <v>169</v>
       </c>
-      <c r="C16">
+      <c r="C20">
         <v>0.908</v>
       </c>
-      <c r="D16">
+      <c r="D20">
         <v>0.061</v>
       </c>
-      <c r="E16">
+      <c r="E20">
         <v>0.884</v>
       </c>
-      <c r="F16">
+      <c r="F20">
         <v>0.091</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
-      <c r="B17" t="s">
+    <row r="21" spans="1:6">
+      <c r="B21" t="s">
         <v>170</v>
       </c>
-      <c r="C17">
+      <c r="C21">
+        <v>0.907</v>
+      </c>
+      <c r="D21">
+        <v>0.024</v>
+      </c>
+      <c r="E21">
+        <v>0.869</v>
+      </c>
+      <c r="F21">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22">
         <v>0.914</v>
       </c>
-      <c r="D17">
+      <c r="D22">
         <v>0.127</v>
       </c>
-      <c r="E17">
+      <c r="E22">
         <v>0.871</v>
       </c>
-      <c r="F17">
+      <c r="F22">
         <v>0.076</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
-      <c r="B18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18">
+    <row r="23" spans="1:6">
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23">
         <v>0.863</v>
       </c>
-      <c r="D18">
+      <c r="D23">
         <v>0.073</v>
       </c>
-      <c r="E18">
+      <c r="E23">
         <v>0.865</v>
       </c>
-      <c r="F18">
+      <c r="F23">
         <v>0.074</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
-      <c r="B19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19">
+    <row r="24" spans="1:6">
+      <c r="B24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24">
+        <v>0.908</v>
+      </c>
+      <c r="D24">
+        <v>0.067</v>
+      </c>
+      <c r="E24">
+        <v>0.897</v>
+      </c>
+      <c r="F24">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="B25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25">
         <v>0.856</v>
       </c>
-      <c r="D19">
+      <c r="D25">
         <v>0.073</v>
       </c>
-      <c r="E19">
+      <c r="E25">
         <v>0.86</v>
       </c>
-      <c r="F19">
+      <c r="F25">
         <v>0.074</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="A18:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2635,7 +3149,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2646,22 +3160,22 @@
         <v>166</v>
       </c>
       <c r="D1" t="s">
-        <v>326</v>
+        <v>380</v>
       </c>
       <c r="E1" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="F1" t="s">
-        <v>328</v>
+        <v>382</v>
       </c>
       <c r="G1" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="H1" t="s">
-        <v>330</v>
+        <v>384</v>
       </c>
       <c r="I1" t="s">
-        <v>331</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2672,13 +3186,13 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>386</v>
       </c>
       <c r="D2">
         <v>0.007</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="F2">
         <v>0.788</v>
@@ -2687,7 +3201,7 @@
         <v>-0.002</v>
       </c>
       <c r="H2" t="s">
-        <v>352</v>
+        <v>413</v>
       </c>
       <c r="I2">
         <v>0.766</v>
@@ -2701,13 +3215,13 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="D3">
         <v>-0.008</v>
       </c>
       <c r="E3" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="F3">
         <v>0.632</v>
@@ -2716,7 +3230,7 @@
         <v>-0.013</v>
       </c>
       <c r="H3" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="I3">
         <v>0.11</v>
@@ -2730,25 +3244,25 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>334</v>
+        <v>388</v>
       </c>
       <c r="D4">
-        <v>-0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="E4" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="F4">
-        <v>0.366</v>
+        <v>0.826</v>
       </c>
       <c r="G4">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H4" t="s">
-        <v>354</v>
+        <v>415</v>
       </c>
       <c r="I4">
-        <v>0.304</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2759,25 +3273,25 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>335</v>
+        <v>389</v>
       </c>
       <c r="D5">
-        <v>-0.044</v>
+        <v>-0.015</v>
       </c>
       <c r="E5" t="s">
-        <v>340</v>
+        <v>396</v>
       </c>
       <c r="F5">
-        <v>0.23</v>
+        <v>0.366</v>
       </c>
       <c r="G5">
-        <v>-0.012</v>
+        <v>0.004</v>
       </c>
       <c r="H5" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="I5">
-        <v>0.102</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2788,25 +3302,25 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="D6">
-        <v>-0.033</v>
+        <v>-0.044</v>
       </c>
       <c r="E6" t="s">
-        <v>341</v>
+        <v>397</v>
       </c>
       <c r="F6">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="G6">
-        <v>-0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="H6" t="s">
-        <v>356</v>
+        <v>417</v>
       </c>
       <c r="I6">
-        <v>0.296</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2814,28 +3328,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="D7">
-        <v>0.031</v>
+        <v>-0.016</v>
       </c>
       <c r="E7" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="F7">
-        <v>0.26</v>
+        <v>0.394</v>
       </c>
       <c r="G7">
-        <v>-0</v>
+        <v>-0.008</v>
       </c>
       <c r="H7" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="I7">
-        <v>0.9419999999999999</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2843,28 +3357,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="D8">
-        <v>-0.004</v>
+        <v>-0.033</v>
       </c>
       <c r="E8" t="s">
-        <v>343</v>
+        <v>399</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G8">
-        <v>0.002</v>
+        <v>-0.01</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="I8">
-        <v>0.772</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2875,25 +3389,25 @@
         <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="E9" t="s">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="s">
-        <v>344</v>
+        <v>419</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2904,25 +3418,25 @@
         <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>387</v>
       </c>
       <c r="D10">
-        <v>-0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E10" t="s">
-        <v>345</v>
+        <v>401</v>
       </c>
       <c r="F10">
-        <v>0.918</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>-0.013</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="s">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="I10">
-        <v>0.016</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2933,25 +3447,25 @@
         <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="D11">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>346</v>
+        <v>402</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="I11">
-        <v>0.002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2959,28 +3473,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="D12">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>402</v>
       </c>
       <c r="F12">
-        <v>0.702</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="I12">
-        <v>0.772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2988,28 +3502,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="D13">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" t="s">
-        <v>348</v>
+        <v>403</v>
       </c>
       <c r="F13">
-        <v>0.772</v>
+        <v>0.918</v>
       </c>
       <c r="G13">
-        <v>-0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="H13" t="s">
-        <v>362</v>
+        <v>421</v>
       </c>
       <c r="I13">
-        <v>0.448</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3017,28 +3531,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="D14">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="E14" t="s">
-        <v>349</v>
+        <v>404</v>
       </c>
       <c r="F14">
-        <v>0.966</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="H14" t="s">
-        <v>363</v>
+        <v>422</v>
       </c>
       <c r="I14">
-        <v>0.29</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3046,28 +3560,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="D15">
-        <v>-0.014</v>
+        <v>0.005</v>
       </c>
       <c r="E15" t="s">
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="F15">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>-0.012</v>
+        <v>-0.015</v>
       </c>
       <c r="H15" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="I15">
-        <v>0.312</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -3078,24 +3592,198 @@
         <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="D16">
+        <v>0.013</v>
+      </c>
+      <c r="E16" t="s">
+        <v>406</v>
+      </c>
+      <c r="F16">
+        <v>0.702</v>
+      </c>
+      <c r="G16">
+        <v>-0.004</v>
+      </c>
+      <c r="H16" t="s">
+        <v>424</v>
+      </c>
+      <c r="I16">
+        <v>0.772</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>387</v>
+      </c>
+      <c r="D17">
+        <v>0.015</v>
+      </c>
+      <c r="E17" t="s">
+        <v>407</v>
+      </c>
+      <c r="F17">
+        <v>0.772</v>
+      </c>
+      <c r="G17">
+        <v>-0.004</v>
+      </c>
+      <c r="H17" t="s">
+        <v>425</v>
+      </c>
+      <c r="I17">
+        <v>0.448</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>388</v>
+      </c>
+      <c r="D18">
+        <v>0.017</v>
+      </c>
+      <c r="E18" t="s">
+        <v>408</v>
+      </c>
+      <c r="F18">
+        <v>0.63</v>
+      </c>
+      <c r="G18">
+        <v>0.011</v>
+      </c>
+      <c r="H18" t="s">
+        <v>426</v>
+      </c>
+      <c r="I18">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>389</v>
+      </c>
+      <c r="D19">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E19" t="s">
+        <v>409</v>
+      </c>
+      <c r="F19">
+        <v>0.966</v>
+      </c>
+      <c r="G19">
+        <v>-0.007</v>
+      </c>
+      <c r="H19" t="s">
+        <v>427</v>
+      </c>
+      <c r="I19">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>390</v>
+      </c>
+      <c r="D20">
+        <v>-0.014</v>
+      </c>
+      <c r="E20" t="s">
+        <v>410</v>
+      </c>
+      <c r="F20">
+        <v>0.71</v>
+      </c>
+      <c r="G20">
+        <v>-0.012</v>
+      </c>
+      <c r="H20" t="s">
+        <v>428</v>
+      </c>
+      <c r="I20">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>391</v>
+      </c>
+      <c r="D21">
+        <v>0.03</v>
+      </c>
+      <c r="E21" t="s">
+        <v>411</v>
+      </c>
+      <c r="F21">
+        <v>0.42</v>
+      </c>
+      <c r="G21">
+        <v>-0.011</v>
+      </c>
+      <c r="H21" t="s">
+        <v>429</v>
+      </c>
+      <c r="I21">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
+        <v>392</v>
+      </c>
+      <c r="D22">
         <v>-0.01</v>
       </c>
-      <c r="E16" t="s">
-        <v>351</v>
-      </c>
-      <c r="F16">
+      <c r="E22" t="s">
+        <v>412</v>
+      </c>
+      <c r="F22">
         <v>0.778</v>
       </c>
-      <c r="G16">
+      <c r="G22">
         <v>-0.016</v>
       </c>
-      <c r="H16" t="s">
-        <v>365</v>
-      </c>
-      <c r="I16">
+      <c r="H22" t="s">
+        <v>430</v>
+      </c>
+      <c r="I22">
         <v>0.13</v>
       </c>
     </row>
@@ -3111,13 +3799,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>366</v>
+        <v>431</v>
       </c>
       <c r="C1" t="s">
-        <v>367</v>
+        <v>432</v>
       </c>
       <c r="D1" t="s">
-        <v>368</v>
+        <v>433</v>
       </c>
       <c r="E1" t="s">
         <v>157</v>
@@ -3126,10 +3814,10 @@
         <v>166</v>
       </c>
       <c r="G1" t="s">
-        <v>369</v>
+        <v>434</v>
       </c>
       <c r="H1" t="s">
-        <v>370</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3143,13 +3831,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E2" t="s">
         <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="G2">
         <v>0.907</v>
@@ -3169,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E3" t="s">
         <v>54</v>
@@ -3195,13 +3883,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E4" t="s">
         <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="G4">
         <v>0.917</v>
@@ -3221,7 +3909,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E5" t="s">
         <v>54</v>
@@ -3247,13 +3935,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E6" t="s">
         <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="G6">
         <v>0.899</v>
@@ -3273,7 +3961,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E7" t="s">
         <v>54</v>
@@ -3299,19 +3987,19 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E8" t="s">
         <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="G8">
-        <v>0.911</v>
+        <v>0.929</v>
       </c>
       <c r="H8">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3325,7 +4013,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E9" t="s">
         <v>54</v>
@@ -3351,16 +4039,16 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E10" t="s">
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="G10">
-        <v>0.931</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H10">
         <v>0.023</v>
@@ -3377,7 +4065,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -3403,13 +4091,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E12" t="s">
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="G12">
         <v>0.927</v>
@@ -3429,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -3455,13 +4143,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="G14">
         <v>0.913</v>
@@ -3481,7 +4169,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E15" t="s">
         <v>54</v>
@@ -3507,13 +4195,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E16" t="s">
         <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="G16">
         <v>0.918</v>
@@ -3533,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E17" t="s">
         <v>54</v>
@@ -3559,13 +4247,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E18" t="s">
         <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="G18">
         <v>0.915</v>
@@ -3585,7 +4273,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
         <v>54</v>
@@ -3611,13 +4299,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="E20" t="s">
         <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="G20">
         <v>0.907</v>
@@ -3637,7 +4325,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="E21" t="s">
         <v>54</v>
@@ -3664,7 +4352,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>368</v>
+        <v>433</v>
       </c>
       <c r="B1" t="s">
         <v>48</v>
@@ -3687,30 +4375,30 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="B2" t="s">
-        <v>373</v>
+        <v>438</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>439</v>
       </c>
       <c r="D2" t="s">
-        <v>375</v>
+        <v>440</v>
       </c>
       <c r="E2" t="s">
-        <v>376</v>
+        <v>441</v>
       </c>
       <c r="F2" t="s">
-        <v>376</v>
+        <v>441</v>
       </c>
       <c r="G2" t="s">
-        <v>378</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -3722,13 +4410,13 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="F3" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="G3" t="s">
-        <v>379</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -3749,7 +4437,7 @@
         <v>166</v>
       </c>
       <c r="D1" t="s">
-        <v>380</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3760,7 +4448,7 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -3774,10 +4462,10 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3788,10 +4476,10 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3802,7 +4490,7 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3815,7 +4503,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3832,7 +4520,7 @@
         <v>105</v>
       </c>
       <c r="E1" t="s">
-        <v>381</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3888,7 +4576,7 @@
         <v>0.931</v>
       </c>
       <c r="D5">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -3899,10 +4587,10 @@
         <v>171</v>
       </c>
       <c r="C6">
-        <v>0.911</v>
+        <v>0.931</v>
       </c>
       <c r="D6">
-        <v>0.038</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -3913,7 +4601,7 @@
         <v>172</v>
       </c>
       <c r="C7">
-        <v>0.906</v>
+        <v>0.911</v>
       </c>
       <c r="D7">
         <v>0.038</v>
@@ -3923,59 +4611,59 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C8">
-        <v>0.948</v>
+        <v>0.928</v>
       </c>
       <c r="D8">
-        <v>0.035</v>
+        <v>0.053</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C9">
-        <v>0.944</v>
+        <v>0.906</v>
       </c>
       <c r="D9">
-        <v>0.082</v>
+        <v>0.038</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10">
-        <v>0.944</v>
+        <v>0.948</v>
       </c>
       <c r="D10">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11">
-        <v>0.947</v>
+        <v>0.944</v>
       </c>
       <c r="D11">
-        <v>0.036</v>
+        <v>0.082</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -3983,44 +4671,41 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C12">
-        <v>0.9370000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="D12">
-        <v>0.029</v>
+        <v>0.039</v>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C13">
-        <v>0.9320000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="D13">
-        <v>0.03</v>
+        <v>0.037</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>60</v>
-      </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C14">
-        <v>0.904</v>
+        <v>0.947</v>
       </c>
       <c r="D14">
-        <v>0.089</v>
+        <v>0.036</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -4028,79 +4713,166 @@
     </row>
     <row r="15" spans="1:5">
       <c r="B15" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C15">
-        <v>0.901</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="D15">
-        <v>0.09</v>
+        <v>0.029</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C16">
-        <v>0.906</v>
+        <v>0.947</v>
       </c>
       <c r="D16">
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="1:5">
       <c r="B17" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C17">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D17">
-        <v>0.079</v>
+        <v>0.03</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
       <c r="B18" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C18">
-        <v>0.895</v>
+        <v>0.904</v>
       </c>
       <c r="D18">
-        <v>0.022</v>
+        <v>0.089</v>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="B19" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C19">
-        <v>0.892</v>
+        <v>0.901</v>
       </c>
       <c r="D19">
-        <v>0.028</v>
+        <v>0.09</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="1:5">
+      <c r="B20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20">
+        <v>0.906</v>
+      </c>
+      <c r="D20">
+        <v>0.043</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21">
+        <v>0.914</v>
+      </c>
+      <c r="D21">
+        <v>0.05</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22">
+        <v>0.902</v>
+      </c>
+      <c r="D22">
+        <v>0.079</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23">
+        <v>0.895</v>
+      </c>
+      <c r="D23">
+        <v>0.022</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="B24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24">
+        <v>0.902</v>
+      </c>
+      <c r="D24">
+        <v>0.056</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25">
+        <v>0.892</v>
+      </c>
+      <c r="D25">
+        <v>0.028</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="A18:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4108,7 +4880,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4116,7 +4888,7 @@
         <v>157</v>
       </c>
       <c r="C1" t="s">
-        <v>382</v>
+        <v>447</v>
       </c>
       <c r="D1" t="s">
         <v>166</v>
@@ -4183,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="E3">
         <v>0.909</v>
@@ -4212,28 +4984,28 @@
         <v>54</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>388</v>
       </c>
       <c r="E4">
-        <v>0.914</v>
+        <v>0.915</v>
       </c>
       <c r="F4">
-        <v>0.083</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G4">
-        <v>0.905</v>
+        <v>0.898</v>
       </c>
       <c r="H4">
-        <v>0.926</v>
+        <v>0.921</v>
       </c>
       <c r="I4">
-        <v>0.823</v>
+        <v>0.827</v>
       </c>
       <c r="J4">
-        <v>0.907</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4247,25 +5019,25 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="E5">
-        <v>0.902</v>
+        <v>0.914</v>
       </c>
       <c r="F5">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="G5">
-        <v>0.898</v>
+        <v>0.905</v>
       </c>
       <c r="H5">
-        <v>0.921</v>
+        <v>0.926</v>
       </c>
       <c r="I5">
-        <v>0.869</v>
+        <v>0.823</v>
       </c>
       <c r="J5">
-        <v>0.891</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4276,28 +5048,28 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="E6">
-        <v>0.906</v>
+        <v>0.902</v>
       </c>
       <c r="F6">
-        <v>0.104</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G6">
-        <v>0.915</v>
+        <v>0.898</v>
       </c>
       <c r="H6">
-        <v>0.9320000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="I6">
-        <v>0.8159999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="J6">
-        <v>0.89</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4308,28 +5080,28 @@
         <v>54</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="E7">
-        <v>0.876</v>
+        <v>0.912</v>
       </c>
       <c r="F7">
-        <v>0.172</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G7">
-        <v>0.907</v>
+        <v>0.897</v>
       </c>
       <c r="H7">
-        <v>0.927</v>
+        <v>0.919</v>
       </c>
       <c r="I7">
-        <v>0.86</v>
+        <v>0.827</v>
       </c>
       <c r="J7">
-        <v>0.844</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4340,28 +5112,28 @@
         <v>54</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>167</v>
       </c>
       <c r="E8">
-        <v>0.885</v>
+        <v>0.906</v>
       </c>
       <c r="F8">
-        <v>0.151</v>
+        <v>0.104</v>
       </c>
       <c r="G8">
-        <v>0.929</v>
+        <v>0.915</v>
       </c>
       <c r="H8">
-        <v>0.9389999999999999</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I8">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="J8">
-        <v>0.851</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4372,28 +5144,28 @@
         <v>54</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="E9">
-        <v>0.833</v>
+        <v>0.876</v>
       </c>
       <c r="F9">
-        <v>0.332</v>
+        <v>0.172</v>
       </c>
       <c r="G9">
-        <v>0.919</v>
+        <v>0.907</v>
       </c>
       <c r="H9">
-        <v>0.9320000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="I9">
-        <v>0.884</v>
+        <v>0.86</v>
       </c>
       <c r="J9">
-        <v>0.771</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4401,31 +5173,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>388</v>
       </c>
       <c r="E10">
-        <v>0.9399999999999999</v>
+        <v>0.898</v>
       </c>
       <c r="F10">
-        <v>0.035</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G10">
-        <v>0.9320000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="H10">
-        <v>0.947</v>
+        <v>0.917</v>
       </c>
       <c r="I10">
-        <v>0.897</v>
+        <v>0.821</v>
       </c>
       <c r="J10">
-        <v>0.9360000000000001</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4433,31 +5205,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="E11">
-        <v>0.9379999999999999</v>
+        <v>0.885</v>
       </c>
       <c r="F11">
-        <v>0.039</v>
+        <v>0.151</v>
       </c>
       <c r="G11">
-        <v>0.9320000000000001</v>
+        <v>0.929</v>
       </c>
       <c r="H11">
-        <v>0.947</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="I11">
-        <v>0.903</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J11">
-        <v>0.9320000000000001</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4465,31 +5237,31 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="E12">
-        <v>0.926</v>
+        <v>0.833</v>
       </c>
       <c r="F12">
-        <v>0.06900000000000001</v>
+        <v>0.332</v>
       </c>
       <c r="G12">
+        <v>0.919</v>
+      </c>
+      <c r="H12">
         <v>0.9320000000000001</v>
       </c>
-      <c r="H12">
-        <v>0.947</v>
-      </c>
       <c r="I12">
-        <v>0.863</v>
+        <v>0.884</v>
       </c>
       <c r="J12">
-        <v>0.912</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4497,31 +5269,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="E13">
-        <v>0.927</v>
+        <v>0.888</v>
       </c>
       <c r="F13">
-        <v>0.057</v>
+        <v>0.112</v>
       </c>
       <c r="G13">
-        <v>0.9320000000000001</v>
+        <v>0.886</v>
       </c>
       <c r="H13">
-        <v>0.947</v>
+        <v>0.911</v>
       </c>
       <c r="I13">
-        <v>0.882</v>
+        <v>0.774</v>
       </c>
       <c r="J13">
-        <v>0.914</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4532,28 +5304,28 @@
         <v>56</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
         <v>167</v>
       </c>
       <c r="E14">
-        <v>0.904</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F14">
-        <v>0.129</v>
+        <v>0.035</v>
       </c>
       <c r="G14">
         <v>0.9320000000000001</v>
       </c>
       <c r="H14">
-        <v>0.944</v>
+        <v>0.947</v>
       </c>
       <c r="I14">
-        <v>0.803</v>
+        <v>0.897</v>
       </c>
       <c r="J14">
-        <v>0.878</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4564,28 +5336,28 @@
         <v>56</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="E15">
-        <v>0.908</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F15">
-        <v>0.094</v>
+        <v>0.039</v>
       </c>
       <c r="G15">
-        <v>0.931</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H15">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="I15">
-        <v>0.848</v>
+        <v>0.903</v>
       </c>
       <c r="J15">
-        <v>0.884</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4596,28 +5368,28 @@
         <v>56</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>388</v>
       </c>
       <c r="E16">
-        <v>0.885</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F16">
-        <v>0.16</v>
+        <v>0.037</v>
       </c>
       <c r="G16">
-        <v>0.9370000000000001</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H16">
-        <v>0.948</v>
+        <v>0.947</v>
       </c>
       <c r="I16">
-        <v>0.777</v>
+        <v>0.895</v>
       </c>
       <c r="J16">
-        <v>0.846</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4628,28 +5400,28 @@
         <v>56</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="E17">
-        <v>0.886</v>
+        <v>0.926</v>
       </c>
       <c r="F17">
-        <v>0.14</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G17">
         <v>0.9320000000000001</v>
       </c>
       <c r="H17">
-        <v>0.944</v>
+        <v>0.947</v>
       </c>
       <c r="I17">
-        <v>0.829</v>
+        <v>0.863</v>
       </c>
       <c r="J17">
-        <v>0.849</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4657,31 +5429,31 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="E18">
-        <v>0.902</v>
+        <v>0.927</v>
       </c>
       <c r="F18">
-        <v>0.089</v>
+        <v>0.057</v>
       </c>
       <c r="G18">
-        <v>0.917</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H18">
-        <v>0.905</v>
+        <v>0.947</v>
       </c>
       <c r="I18">
-        <v>0.871</v>
+        <v>0.882</v>
       </c>
       <c r="J18">
-        <v>0.9</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4689,31 +5461,31 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="E19">
-        <v>0.903</v>
+        <v>0.929</v>
       </c>
       <c r="F19">
-        <v>0.043</v>
+        <v>0.06</v>
       </c>
       <c r="G19">
-        <v>0.908</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H19">
-        <v>0.915</v>
+        <v>0.948</v>
       </c>
       <c r="I19">
-        <v>0.884</v>
+        <v>0.874</v>
       </c>
       <c r="J19">
-        <v>0.896</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4721,31 +5493,31 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
         <v>167</v>
       </c>
       <c r="E20">
-        <v>0.882</v>
+        <v>0.904</v>
       </c>
       <c r="F20">
-        <v>0.122</v>
+        <v>0.129</v>
       </c>
       <c r="G20">
-        <v>0.924</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H20">
-        <v>0.895</v>
+        <v>0.944</v>
       </c>
       <c r="I20">
-        <v>0.839</v>
+        <v>0.803</v>
       </c>
       <c r="J20">
-        <v>0.873</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4753,31 +5525,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="E21">
+        <v>0.908</v>
+      </c>
+      <c r="F21">
+        <v>0.094</v>
+      </c>
+      <c r="G21">
+        <v>0.931</v>
+      </c>
+      <c r="H21">
+        <v>0.946</v>
+      </c>
+      <c r="I21">
+        <v>0.848</v>
+      </c>
+      <c r="J21">
         <v>0.884</v>
-      </c>
-      <c r="F21">
-        <v>0.079</v>
-      </c>
-      <c r="G21">
-        <v>0.919</v>
-      </c>
-      <c r="H21">
-        <v>0.914</v>
-      </c>
-      <c r="I21">
-        <v>0.855</v>
-      </c>
-      <c r="J21">
-        <v>0.866</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4785,31 +5557,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C22">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>167</v>
+        <v>388</v>
       </c>
       <c r="E22">
-        <v>0.854</v>
+        <v>0.914</v>
       </c>
       <c r="F22">
-        <v>0.157</v>
+        <v>0.09</v>
       </c>
       <c r="G22">
-        <v>0.9360000000000001</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H22">
-        <v>0.902</v>
+        <v>0.947</v>
       </c>
       <c r="I22">
-        <v>0.779</v>
+        <v>0.85</v>
       </c>
       <c r="J22">
-        <v>0.824</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4817,31 +5589,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C23">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="E23">
-        <v>0.858</v>
+        <v>0.885</v>
       </c>
       <c r="F23">
-        <v>0.112</v>
+        <v>0.16</v>
       </c>
       <c r="G23">
-        <v>0.929</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H23">
-        <v>0.913</v>
+        <v>0.948</v>
       </c>
       <c r="I23">
-        <v>0.824</v>
+        <v>0.777</v>
       </c>
       <c r="J23">
-        <v>0.823</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4849,31 +5621,31 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C24">
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="E24">
-        <v>0.825</v>
+        <v>0.886</v>
       </c>
       <c r="F24">
-        <v>0.154</v>
+        <v>0.14</v>
       </c>
       <c r="G24">
-        <v>0.924</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H24">
-        <v>0.875</v>
+        <v>0.944</v>
       </c>
       <c r="I24">
-        <v>0.789</v>
+        <v>0.829</v>
       </c>
       <c r="J24">
-        <v>0.792</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4881,31 +5653,415 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="E25">
+        <v>0.894</v>
+      </c>
+      <c r="F25">
+        <v>0.125</v>
+      </c>
+      <c r="G25">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="H25">
+        <v>0.946</v>
+      </c>
+      <c r="I25">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="J25">
+        <v>0.861</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26">
+        <v>0.902</v>
+      </c>
+      <c r="F26">
+        <v>0.089</v>
+      </c>
+      <c r="G26">
+        <v>0.917</v>
+      </c>
+      <c r="H26">
+        <v>0.905</v>
+      </c>
+      <c r="I26">
+        <v>0.871</v>
+      </c>
+      <c r="J26">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>387</v>
+      </c>
+      <c r="E27">
+        <v>0.903</v>
+      </c>
+      <c r="F27">
+        <v>0.043</v>
+      </c>
+      <c r="G27">
+        <v>0.908</v>
+      </c>
+      <c r="H27">
+        <v>0.915</v>
+      </c>
+      <c r="I27">
+        <v>0.884</v>
+      </c>
+      <c r="J27">
+        <v>0.896</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>388</v>
+      </c>
+      <c r="E28">
+        <v>0.908</v>
+      </c>
+      <c r="F28">
+        <v>0.05</v>
+      </c>
+      <c r="G28">
+        <v>0.907</v>
+      </c>
+      <c r="H28">
+        <v>0.922</v>
+      </c>
+      <c r="I28">
+        <v>0.869</v>
+      </c>
+      <c r="J28">
+        <v>0.899</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29">
+        <v>50</v>
+      </c>
+      <c r="D29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29">
+        <v>0.882</v>
+      </c>
+      <c r="F29">
+        <v>0.122</v>
+      </c>
+      <c r="G29">
+        <v>0.924</v>
+      </c>
+      <c r="H29">
+        <v>0.895</v>
+      </c>
+      <c r="I29">
+        <v>0.839</v>
+      </c>
+      <c r="J29">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
+        <v>387</v>
+      </c>
+      <c r="E30">
+        <v>0.884</v>
+      </c>
+      <c r="F30">
+        <v>0.079</v>
+      </c>
+      <c r="G30">
+        <v>0.919</v>
+      </c>
+      <c r="H30">
+        <v>0.914</v>
+      </c>
+      <c r="I30">
+        <v>0.855</v>
+      </c>
+      <c r="J30">
+        <v>0.866</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31">
+        <v>50</v>
+      </c>
+      <c r="D31" t="s">
+        <v>388</v>
+      </c>
+      <c r="E31">
+        <v>0.893</v>
+      </c>
+      <c r="F31">
+        <v>0.089</v>
+      </c>
+      <c r="G31">
+        <v>0.907</v>
+      </c>
+      <c r="H31">
+        <v>0.919</v>
+      </c>
+      <c r="I31">
+        <v>0.842</v>
+      </c>
+      <c r="J31">
+        <v>0.876</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32">
+        <v>0.854</v>
+      </c>
+      <c r="F32">
+        <v>0.157</v>
+      </c>
+      <c r="G32">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="H32">
+        <v>0.902</v>
+      </c>
+      <c r="I32">
+        <v>0.779</v>
+      </c>
+      <c r="J32">
+        <v>0.824</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>387</v>
+      </c>
+      <c r="E33">
+        <v>0.858</v>
+      </c>
+      <c r="F33">
+        <v>0.112</v>
+      </c>
+      <c r="G33">
+        <v>0.929</v>
+      </c>
+      <c r="H33">
+        <v>0.913</v>
+      </c>
+      <c r="I33">
+        <v>0.824</v>
+      </c>
+      <c r="J33">
+        <v>0.823</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>388</v>
+      </c>
+      <c r="E34">
+        <v>0.868</v>
+      </c>
+      <c r="F34">
+        <v>0.137</v>
+      </c>
+      <c r="G34">
+        <v>0.915</v>
+      </c>
+      <c r="H34">
+        <v>0.921</v>
+      </c>
+      <c r="I34">
+        <v>0.79</v>
+      </c>
+      <c r="J34">
+        <v>0.834</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35">
+        <v>0.825</v>
+      </c>
+      <c r="F35">
+        <v>0.154</v>
+      </c>
+      <c r="G35">
+        <v>0.924</v>
+      </c>
+      <c r="H35">
+        <v>0.875</v>
+      </c>
+      <c r="I35">
+        <v>0.789</v>
+      </c>
+      <c r="J35">
+        <v>0.792</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>387</v>
+      </c>
+      <c r="E36">
         <v>0.8090000000000001</v>
       </c>
-      <c r="F25">
+      <c r="F36">
         <v>0.131</v>
       </c>
-      <c r="G25">
+      <c r="G36">
         <v>0.92</v>
       </c>
-      <c r="H25">
+      <c r="H36">
         <v>0.881</v>
       </c>
-      <c r="I25">
+      <c r="I36">
         <v>0.823</v>
       </c>
-      <c r="J25">
+      <c r="J36">
         <v>0.764</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>388</v>
+      </c>
+      <c r="E37">
+        <v>0.84</v>
+      </c>
+      <c r="F37">
+        <v>0.144</v>
+      </c>
+      <c r="G37">
+        <v>0.9</v>
+      </c>
+      <c r="H37">
+        <v>0.897</v>
+      </c>
+      <c r="I37">
+        <v>0.756</v>
+      </c>
+      <c r="J37">
+        <v>0.805</v>
       </c>
     </row>
   </sheetData>
@@ -4926,7 +6082,7 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>383</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5067,6 +6223,72 @@
       </c>
       <c r="D11">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>3.92</v>
+      </c>
+      <c r="D2">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>3.68</v>
+      </c>
+      <c r="D3">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>3.8</v>
+      </c>
+      <c r="D4">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
